--- a/Aug_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
+++ b/Aug_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD859F01-FABE-4806-86EA-56099E7F007A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD78DE78-FF78-4252-8AD3-9934E536B7C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
